--- a/test/appn-embedded.xlsx
+++ b/test/appn-embedded.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t xml:space="preserve">http://purl.obolibrary.org/obo/TO_0002756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grain</t>
   </si>
 </sst>
 </file>
@@ -731,7 +734,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>15</v>
@@ -837,7 +840,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H1003" type="list">
-      <formula1>#REF!</formula1>
+      <formula1>#ref!</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
